--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_PROINBENI UPB GANDIA.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_PROINBENI UPB GANDIA.xlsx
@@ -565,67 +565,67 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>7.212199999999999</v>
+        <v>7.293</v>
       </c>
       <c r="E2" t="n">
-        <v>5.333600000000001</v>
+        <v>5.6684</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8785</v>
+        <v>1.6246</v>
       </c>
       <c r="G2" t="n">
-        <v>1.8811</v>
+        <v>1.965</v>
       </c>
       <c r="H2" t="n">
-        <v>2.4488</v>
+        <v>2.545</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5677000000000001</v>
+        <v>-0.5801000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>6.6114</v>
+        <v>6.8357</v>
       </c>
       <c r="K2" t="n">
-        <v>4.7357</v>
+        <v>4.913</v>
       </c>
       <c r="L2" t="n">
-        <v>1.8757</v>
+        <v>1.9227</v>
       </c>
       <c r="M2" t="n">
-        <v>-4.7303</v>
+        <v>-4.8707</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.2869</v>
+        <v>-2.3679</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.4434</v>
+        <v>-2.5028</v>
       </c>
       <c r="P2" t="n">
-        <v>4.9164</v>
+        <v>4.8588</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.229</v>
+        <v>-1.2148</v>
       </c>
       <c r="R2" t="n">
-        <v>6.1454</v>
+        <v>6.0736</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.5368</v>
+        <v>-2.5062</v>
       </c>
       <c r="T2" t="n">
-        <v>-2.652</v>
+        <v>-2.5839</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1152</v>
+        <v>0.0776</v>
       </c>
       <c r="V2" t="n">
-        <v>2.9515</v>
+        <v>2.9755</v>
       </c>
       <c r="W2" t="n">
-        <v>2.6033</v>
+        <v>2.6313</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3482</v>
+        <v>0.3442</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3754</v>
+        <v>4.3503</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3766</v>
+        <v>4.4536</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.001100000000000101</v>
+        <v>-0.1032999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6533</v>
+        <v>1.674</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4180999999999999</v>
+        <v>-0.4153</v>
       </c>
       <c r="I3" t="n">
-        <v>2.0714</v>
+        <v>2.0893</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9329</v>
+        <v>3.0074</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.5913</v>
       </c>
       <c r="L3" t="n">
-        <v>2.375</v>
+        <v>2.416</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.2796</v>
+        <v>-1.3333</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9761000000000001</v>
+        <v>-1.0066</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3035</v>
+        <v>-0.3268</v>
       </c>
       <c r="P3" t="n">
-        <v>2.2533</v>
+        <v>2.227</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2533</v>
+        <v>2.227</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9529</v>
+        <v>0.9513</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4437</v>
+        <v>1.4463</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4908</v>
+        <v>-0.4951</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.4841000000000001</v>
+        <v>-0.5018999999999999</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.4841000000000001</v>
+        <v>-0.5018999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6239</v>
+        <v>2.5765</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4572</v>
+        <v>3.5979</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8332999999999999</v>
+        <v>-1.0215</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7181</v>
+        <v>2.6927</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.304</v>
+        <v>-0.3156</v>
       </c>
       <c r="I4" t="n">
-        <v>3.022</v>
+        <v>3.0083</v>
       </c>
       <c r="J4" t="n">
-        <v>5.946199999999999</v>
+        <v>6.0312</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1778</v>
+        <v>2.231</v>
       </c>
       <c r="L4" t="n">
-        <v>3.7684</v>
+        <v>3.8003</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.2281</v>
+        <v>-3.3386</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.4818</v>
+        <v>-2.5467</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7464000000000001</v>
+        <v>-0.7918000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8193999999999999</v>
+        <v>0.8098</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2533</v>
+        <v>-2.227</v>
       </c>
       <c r="R4" t="n">
-        <v>3.0727</v>
+        <v>3.0368</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4293000000000001</v>
+        <v>-0.4241</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2356</v>
+        <v>-0.2063</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1937</v>
+        <v>-0.2177999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.4842</v>
+        <v>-0.5018</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.4842</v>
+        <v>-0.5018</v>
       </c>
     </row>
     <row r="5">
@@ -799,73 +799,73 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3175</v>
+        <v>2.3435</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6818000000000002</v>
+        <v>0.8639999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6356</v>
+        <v>1.4795</v>
       </c>
       <c r="G5" t="n">
-        <v>1.425</v>
+        <v>1.42</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7837000000000001</v>
+        <v>-0.8091999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>2.2086</v>
+        <v>2.2292</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2397</v>
+        <v>3.3269</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5865</v>
+        <v>1.6192</v>
       </c>
       <c r="L5" t="n">
-        <v>1.6532</v>
+        <v>1.7077</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8147</v>
+        <v>-1.9069</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.3702</v>
+        <v>-2.4284</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5555000000000001</v>
+        <v>0.5215</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.6388</v>
+        <v>-1.6196</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.097</v>
+        <v>-4.049</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4582</v>
+        <v>2.4294</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5265</v>
+        <v>-0.5256</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4737999999999999</v>
+        <v>-0.4500999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.05260000000000004</v>
+        <v>-0.07550000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>3.0576</v>
+        <v>3.0688</v>
       </c>
       <c r="W5" t="n">
-        <v>2.013</v>
+        <v>2.0362</v>
       </c>
       <c r="X5" t="n">
-        <v>1.0447</v>
+        <v>1.0325</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MOLINA MARTINEZ</t>
+          <t>J. BARBER TERRADES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.02850000000000008</v>
+        <v>-0.064</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.758</v>
+        <v>-0.064</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7296</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.6145</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.9069</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.7076</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6931</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1287</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.8218</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.9214</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.0356</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8857999999999999</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.0485</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.0727</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>5.1212</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1893</v>
+        <v>-0.064</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5851000000000001</v>
+        <v>-0.064</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6042</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3482</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4227</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. BARBER TERRADES</t>
+          <t>J. MOLINA MARTINEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0655</v>
+        <v>-0.0796</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0655</v>
+        <v>-1.5899</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1.5104</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-3.6394</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>-1.9357</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-1.7037</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-0.6167</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.1567</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.7734</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-3.0227</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-2.0924</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0.9303</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.0245</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-3.0368</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>5.061299999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0655</v>
+        <v>1.1911</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0655</v>
+        <v>0.6223</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.5688</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.3442</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.4411</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.0969</v>
       </c>
     </row>
     <row r="8">
@@ -1033,64 +1033,64 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4381</v>
+        <v>-1.4449</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.3064</v>
+        <v>-4.2361</v>
       </c>
       <c r="F8" t="n">
-        <v>2.8682</v>
+        <v>2.7912</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.359</v>
+        <v>-2.3531</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.9522</v>
+        <v>-3.9345</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5932</v>
+        <v>1.5815</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.7668</v>
+        <v>-2.7257</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.478</v>
+        <v>-3.4413</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7113</v>
+        <v>0.7156</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4078000000000001</v>
+        <v>0.3727</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4742</v>
+        <v>-0.4932</v>
       </c>
       <c r="O8" t="n">
-        <v>0.882</v>
+        <v>0.866</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2533</v>
+        <v>2.227</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2533</v>
+        <v>2.227</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6361</v>
+        <v>-0.6305000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8431</v>
+        <v>-0.8221000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2071</v>
+        <v>0.1916</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6965</v>
+        <v>-0.6883</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6965</v>
+        <v>-0.6883</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,67 +1111,67 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0621</v>
+        <v>-2.1169</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6229</v>
+        <v>-1.5501</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4392</v>
+        <v>-0.5668</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9594</v>
+        <v>-2.0044</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9175</v>
+        <v>-0.9474</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0419</v>
+        <v>-1.0572</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7075999999999999</v>
+        <v>-0.6913</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4488</v>
+        <v>0.4544</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.1565</v>
+        <v>-1.1457</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2518</v>
+        <v>-1.3132</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3663</v>
+        <v>-1.4017</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1144999999999999</v>
+        <v>0.08849999999999991</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8436</v>
+        <v>1.8221</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3685</v>
+        <v>1.3531</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9767999999999999</v>
+        <v>0.9876999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3917</v>
+        <v>0.3654000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.4227</v>
+        <v>-1.4411</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2545</v>
+        <v>-2.1922</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.6909</v>
+        <v>-4.4183</v>
       </c>
       <c r="F10" t="n">
-        <v>2.4363</v>
+        <v>2.2261</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3053999999999999</v>
+        <v>0.3215999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.6383</v>
+        <v>-4.6449</v>
       </c>
       <c r="I10" t="n">
-        <v>4.9436</v>
+        <v>4.9665</v>
       </c>
       <c r="J10" t="n">
-        <v>3.8729</v>
+        <v>3.9985</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.7697</v>
+        <v>-2.7111</v>
       </c>
       <c r="L10" t="n">
-        <v>6.6426</v>
+        <v>6.7096</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.5675</v>
+        <v>-3.677</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.8685</v>
+        <v>-1.9338</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.6989</v>
+        <v>-1.7431</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="Q10" t="n">
-        <v>-7.374499999999999</v>
+        <v>-7.2883</v>
       </c>
       <c r="R10" t="n">
-        <v>5.326</v>
+        <v>5.2638</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.45</v>
+        <v>-1.4285</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.4312</v>
+        <v>-1.3795</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.01879999999999993</v>
+        <v>-0.04890000000000005</v>
       </c>
       <c r="V10" t="n">
-        <v>0.9386</v>
+        <v>0.9392</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6965</v>
+        <v>0.6883</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2879</v>
+        <v>-4.3011</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7865</v>
+        <v>-2.7016</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5015</v>
+        <v>-1.5995</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.6364</v>
+        <v>-5.649</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.0983</v>
+        <v>-1.1066</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.5381</v>
+        <v>-4.5426</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.3994</v>
+        <v>-3.3621</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6519</v>
+        <v>-0.6335</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.7475</v>
+        <v>-2.7286</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.237</v>
+        <v>-2.287</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4464</v>
+        <v>-0.4730000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.7906</v>
+        <v>-1.8139</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.229</v>
+        <v>-1.2148</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6387</v>
+        <v>1.6197</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6968</v>
+        <v>0.6920999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4193999999999999</v>
+        <v>0.4339999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2774</v>
+        <v>0.2581000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2421000000000001</v>
+        <v>0.2508999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>1.4227</v>
+        <v>1.4411</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.529100000000001</v>
+        <v>-4.4969</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.3863</v>
+        <v>-4.223</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1427999999999999</v>
+        <v>-0.2738999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.104299999999999</v>
+        <v>-4.0893</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.9607</v>
+        <v>-3.9538</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1435999999999997</v>
+        <v>-0.1355</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.6473</v>
+        <v>-2.5549</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.4828</v>
+        <v>-2.4339</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.1645000000000001</v>
+        <v>-0.121</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.457</v>
+        <v>-1.5344</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.478</v>
+        <v>-1.5199</v>
       </c>
       <c r="O12" t="n">
-        <v>0.02099999999999991</v>
+        <v>-0.01439999999999997</v>
       </c>
       <c r="P12" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R12" t="n">
-        <v>2.663</v>
+        <v>2.6319</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.3057</v>
+        <v>-2.2782</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.441</v>
+        <v>-1.4087</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8648</v>
+        <v>-0.8694999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="W12" t="n">
-        <v>0.7262</v>
+        <v>0.7528</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.4841</v>
+        <v>-0.5019</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.5213</v>
+        <v>-5.587</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.1503</v>
+        <v>-5.990600000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6290000000000001</v>
+        <v>0.4036000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-8.426400000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.9799</v>
+        <v>-3.9547</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.4465</v>
+        <v>-4.4717</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.383699999999999</v>
+        <v>-5.2806</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.0313</v>
+        <v>-2.9495</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.3523</v>
+        <v>-2.3311</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.0427</v>
+        <v>-3.1459</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9486</v>
+        <v>-1.0052</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.0941</v>
+        <v>-2.1407</v>
       </c>
       <c r="P13" t="n">
-        <v>2.8679</v>
+        <v>2.8343</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2533</v>
+        <v>-2.227</v>
       </c>
       <c r="R13" t="n">
-        <v>5.1212</v>
+        <v>5.061299999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5511</v>
+        <v>0.5715</v>
       </c>
       <c r="T13" t="n">
-        <v>1.4867</v>
+        <v>1.5169</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9357</v>
+        <v>-0.9453</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.5137999999999999</v>
+        <v>-0.5663</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5137999999999999</v>
+        <v>-0.5663</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.658000000000006</v>
+        <v>-3.719300000000002</v>
       </c>
       <c r="E14" t="n">
-        <v>-11.9176</v>
+        <v>-10.1897</v>
       </c>
       <c r="F14" t="n">
-        <v>8.2593</v>
+        <v>6.4704</v>
       </c>
       <c r="G14" t="n">
-        <v>-18.1171</v>
+        <v>-18.0883</v>
       </c>
       <c r="H14" t="n">
-        <v>-19.5108</v>
+        <v>-19.4727</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3934</v>
+        <v>1.383999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>7.005200000000002</v>
+        <v>7.968400000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.778200000000001</v>
+        <v>-2.203699999999998</v>
       </c>
       <c r="L14" t="n">
-        <v>9.7836</v>
+        <v>10.1721</v>
       </c>
       <c r="M14" t="n">
-        <v>-25.1223</v>
+        <v>-26.057</v>
       </c>
       <c r="N14" t="n">
-        <v>-16.7326</v>
+        <v>-17.2688</v>
       </c>
       <c r="O14" t="n">
-        <v>-8.389699999999999</v>
+        <v>-8.787800000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>12.2909</v>
+        <v>12.1471</v>
       </c>
       <c r="Q14" t="n">
-        <v>-25.6057</v>
+        <v>-25.3068</v>
       </c>
       <c r="R14" t="n">
-        <v>37.89660000000001</v>
+        <v>37.4539</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.1913</v>
+        <v>-3.098</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.2305</v>
+        <v>-1.9074</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9608000000000001</v>
+        <v>-1.1906</v>
       </c>
       <c r="V14" t="n">
-        <v>5.3594</v>
+        <v>5.3203</v>
       </c>
       <c r="W14" t="n">
-        <v>8.914099999999999</v>
+        <v>9.055300000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.554600000000001</v>
+        <v>-3.7351</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_PROINBENI UPB GANDIA.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_PROINBENI UPB GANDIA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X14"/>
+  <dimension ref="A1:X13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,13 +565,13 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>7.293</v>
+        <v>9.011799999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6684</v>
+        <v>7.2257</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6246</v>
+        <v>1.7861</v>
       </c>
       <c r="G2" t="n">
         <v>1.965</v>
@@ -610,13 +610,13 @@
         <v>6.0736</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.5062</v>
+        <v>-0.7874</v>
       </c>
       <c r="T2" t="n">
-        <v>-2.5839</v>
+        <v>-1.0267</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0776</v>
+        <v>0.2392</v>
       </c>
       <c r="V2" t="n">
         <v>2.9755</v>
@@ -643,13 +643,13 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3503</v>
+        <v>3.7504</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4536</v>
+        <v>3.6231</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1032999999999999</v>
+        <v>0.1272</v>
       </c>
       <c r="G3" t="n">
         <v>1.674</v>
@@ -688,13 +688,13 @@
         <v>2.227</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9513</v>
+        <v>0.3512</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4463</v>
+        <v>0.6157999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4951</v>
+        <v>-0.2646</v>
       </c>
       <c r="V3" t="n">
         <v>-0.5018999999999999</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. SANTANA LUCHORO</t>
+          <t>J. SOLER CIRUJEDA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5765</v>
+        <v>2.9151</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5979</v>
+        <v>1.2396</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.0215</v>
+        <v>1.6755</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6927</v>
+        <v>1.42</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3156</v>
+        <v>-0.8091999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>3.0083</v>
+        <v>2.2292</v>
       </c>
       <c r="J4" t="n">
-        <v>6.0312</v>
+        <v>3.3269</v>
       </c>
       <c r="K4" t="n">
-        <v>2.231</v>
+        <v>1.6192</v>
       </c>
       <c r="L4" t="n">
-        <v>3.8003</v>
+        <v>1.7077</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.3386</v>
+        <v>-1.9069</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.5467</v>
+        <v>-2.4284</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7918000000000001</v>
+        <v>0.5215</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8098</v>
+        <v>-1.6196</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.227</v>
+        <v>-4.049</v>
       </c>
       <c r="R4" t="n">
-        <v>3.0368</v>
+        <v>2.4294</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4241</v>
+        <v>0.0459</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2063</v>
+        <v>-0.0747</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2177999999999999</v>
+        <v>0.1206</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5018</v>
+        <v>3.0688</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.0362</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5018</v>
+        <v>1.0325</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. SOLER CIRUJEDA</t>
+          <t>J. SANTANA LUCHORO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3435</v>
+        <v>2.6117</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8639999999999999</v>
+        <v>3.6621</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4795</v>
+        <v>-1.0503</v>
       </c>
       <c r="G5" t="n">
-        <v>1.42</v>
+        <v>2.6927</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8091999999999999</v>
+        <v>-0.3156</v>
       </c>
       <c r="I5" t="n">
-        <v>2.2292</v>
+        <v>3.0083</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3269</v>
+        <v>6.0312</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6192</v>
+        <v>2.231</v>
       </c>
       <c r="L5" t="n">
-        <v>1.7077</v>
+        <v>3.8003</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.9069</v>
+        <v>-3.3386</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.4284</v>
+        <v>-2.5467</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5215</v>
+        <v>-0.7918000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.6196</v>
+        <v>0.8098</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.049</v>
+        <v>-2.227</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4294</v>
+        <v>3.0368</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5256</v>
+        <v>-0.3889</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4500999999999999</v>
+        <v>-0.1423</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.07550000000000001</v>
+        <v>-0.2467</v>
       </c>
       <c r="V5" t="n">
-        <v>3.0688</v>
+        <v>-0.5018</v>
       </c>
       <c r="W5" t="n">
-        <v>2.0362</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.0325</v>
+        <v>-0.5018</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. BARBER TERRADES</t>
+          <t>J. MOLINA MARTINEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.064</v>
+        <v>-0.5057</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.064</v>
+        <v>-2.1488</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1.6431</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-3.6394</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>-1.9357</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-1.7037</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-0.6167</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.1567</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.7734</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-3.0227</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-2.0924</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.9303</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.0245</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.0368</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>5.061299999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.064</v>
+        <v>0.7651</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.064</v>
+        <v>0.0635</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.7016</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.3442</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.4411</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.0969</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. MOLINA MARTINEZ</t>
+          <t>M. MONTILLA DIAZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0796</v>
+        <v>-1.0463</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5899</v>
+        <v>-3.8607</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5104</v>
+        <v>2.8144</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.6394</v>
+        <v>-2.3531</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.9357</v>
+        <v>-3.9345</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.7037</v>
+        <v>1.5815</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6167</v>
+        <v>-2.7257</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1567</v>
+        <v>-3.4413</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7734</v>
+        <v>0.7156</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.0227</v>
+        <v>0.3727</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.0924</v>
+        <v>-0.4932</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9303</v>
+        <v>0.866</v>
       </c>
       <c r="P7" t="n">
-        <v>2.0245</v>
+        <v>2.227</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.0368</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>5.061299999999999</v>
+        <v>2.227</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1911</v>
+        <v>-0.2319</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6223</v>
+        <v>-0.4466</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5688</v>
+        <v>0.2147</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3442</v>
+        <v>-0.6883</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4411</v>
+        <v>-0.6883</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0969</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. MONTILLA DIAZ</t>
+          <t>L. FERRANDO ORTELLS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4449</v>
+        <v>-1.2686</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.2361</v>
+        <v>-3.6276</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7912</v>
+        <v>2.3589</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.3531</v>
+        <v>0.3215999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.9345</v>
+        <v>-4.6449</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5815</v>
+        <v>4.9665</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.7257</v>
+        <v>3.9985</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.4413</v>
+        <v>-2.7111</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7156</v>
+        <v>6.7096</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3727</v>
+        <v>-3.677</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4932</v>
+        <v>-1.9338</v>
       </c>
       <c r="O8" t="n">
-        <v>0.866</v>
+        <v>-1.7431</v>
       </c>
       <c r="P8" t="n">
-        <v>2.227</v>
+        <v>-2.0245</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-7.2883</v>
       </c>
       <c r="R8" t="n">
-        <v>2.227</v>
+        <v>5.2638</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6305000000000001</v>
+        <v>-0.5048999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8221000000000001</v>
+        <v>-0.5888</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1916</v>
+        <v>0.0838000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6883</v>
+        <v>0.9392</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6883</v>
+        <v>0.2509</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.6883</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. OSAIKHWUWUOMWAN</t>
+          <t>C. HURTADO CERVANTES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1169</v>
+        <v>-2.8235</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5501</v>
+        <v>-2.9531</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5668</v>
+        <v>0.1295000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.0044</v>
+        <v>-4.0893</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9474</v>
+        <v>-3.9538</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0572</v>
+        <v>-0.1355</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6913</v>
+        <v>-2.5549</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4544</v>
+        <v>-2.4339</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.1457</v>
+        <v>-0.121</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3132</v>
+        <v>-1.5344</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4017</v>
+        <v>-1.5199</v>
       </c>
       <c r="O9" t="n">
-        <v>0.08849999999999991</v>
+        <v>-0.01439999999999997</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.2147</v>
+        <v>1.6196</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.0368</v>
+        <v>-1.0123</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8221</v>
+        <v>2.6319</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3531</v>
+        <v>-0.6048</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9876999999999999</v>
+        <v>-0.1387</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3654000000000001</v>
+        <v>-0.466</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2509</v>
+        <v>0.2509</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1902</v>
+        <v>0.7528</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.4411</v>
+        <v>-0.5019</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. FERRANDO ORTELLS</t>
+          <t>C. OSAIKHWUWUOMWAN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1922</v>
+        <v>-3.0677</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.4183</v>
+        <v>-2.2128</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2261</v>
+        <v>-0.8550000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3215999999999999</v>
+        <v>-2.0044</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.6449</v>
+        <v>-0.9474</v>
       </c>
       <c r="I10" t="n">
-        <v>4.9665</v>
+        <v>-1.0572</v>
       </c>
       <c r="J10" t="n">
-        <v>3.9985</v>
+        <v>-0.6913</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.7111</v>
+        <v>0.4544</v>
       </c>
       <c r="L10" t="n">
-        <v>6.7096</v>
+        <v>-1.1457</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.677</v>
+        <v>-1.3132</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.9338</v>
+        <v>-1.4017</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.7431</v>
+        <v>0.08849999999999991</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.0245</v>
+        <v>-1.2147</v>
       </c>
       <c r="Q10" t="n">
-        <v>-7.2883</v>
+        <v>-3.0368</v>
       </c>
       <c r="R10" t="n">
-        <v>5.2638</v>
+        <v>1.8221</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4285</v>
+        <v>0.4023</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.3795</v>
+        <v>0.3251</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.04890000000000005</v>
+        <v>0.07719999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>0.9392</v>
+        <v>-0.2509</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2509</v>
+        <v>1.1902</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6883</v>
+        <v>-1.4411</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3011</v>
+        <v>-4.900700000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7016</v>
+        <v>-3.013</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5995</v>
+        <v>-1.8877</v>
       </c>
       <c r="G11" t="n">
         <v>-5.649</v>
@@ -1312,13 +1312,13 @@
         <v>1.6197</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6920999999999999</v>
+        <v>0.0925</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4339999999999999</v>
+        <v>0.1226</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2581000000000001</v>
+        <v>-0.03010000000000002</v>
       </c>
       <c r="V11" t="n">
         <v>0.2508999999999999</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C. HURTADO CERVANTES</t>
+          <t>J. BITJAA KODY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.4969</v>
+        <v>-6.3711</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.223</v>
+        <v>-7.4838</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2738999999999999</v>
+        <v>1.1128</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.0893</v>
+        <v>-8.426400000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.9538</v>
+        <v>-3.9547</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1355</v>
+        <v>-4.4717</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.5549</v>
+        <v>-5.2806</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.4339</v>
+        <v>-2.9495</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.121</v>
+        <v>-2.3311</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.5344</v>
+        <v>-3.1459</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.5199</v>
+        <v>-1.0052</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.01439999999999997</v>
+        <v>-2.1407</v>
       </c>
       <c r="P12" t="n">
-        <v>1.6196</v>
+        <v>2.8343</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0123</v>
+        <v>-2.227</v>
       </c>
       <c r="R12" t="n">
-        <v>2.6319</v>
+        <v>5.061299999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.2782</v>
+        <v>-0.2126</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.4087</v>
+        <v>0.0237</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8694999999999999</v>
+        <v>-0.2363</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2509</v>
+        <v>-0.5663</v>
       </c>
       <c r="W12" t="n">
-        <v>0.7528</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.5019</v>
+        <v>-0.5663</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. BITJAA KODY</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,144 +1423,66 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.587</v>
+        <v>-1.694599999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.990600000000001</v>
+        <v>-9.549299999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4036000000000001</v>
+        <v>7.854500000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-8.426400000000001</v>
+        <v>-18.0883</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.9547</v>
+        <v>-19.4727</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.4717</v>
+        <v>1.384</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.2806</v>
+        <v>7.968400000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.9495</v>
+        <v>-2.203699999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.3311</v>
+        <v>10.1721</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.1459</v>
+        <v>-26.057</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.0052</v>
+        <v>-17.2688</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.1407</v>
+        <v>-8.787800000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>2.8343</v>
+        <v>12.1471</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.227</v>
+        <v>-25.3068</v>
       </c>
       <c r="R13" t="n">
-        <v>5.061299999999999</v>
+        <v>37.4539</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5715</v>
+        <v>-1.0735</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5169</v>
+        <v>-1.2671</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9453</v>
+        <v>0.1934000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.5663</v>
+        <v>5.3203</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>9.055300000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5663</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>PROINBENI UPB GANDIA</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-3.719300000000002</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-10.1897</v>
-      </c>
-      <c r="F14" t="n">
-        <v>6.4704</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-18.0883</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-19.4727</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1.383999999999999</v>
-      </c>
-      <c r="J14" t="n">
-        <v>7.968400000000001</v>
-      </c>
-      <c r="K14" t="n">
-        <v>-2.203699999999998</v>
-      </c>
-      <c r="L14" t="n">
-        <v>10.1721</v>
-      </c>
-      <c r="M14" t="n">
-        <v>-26.057</v>
-      </c>
-      <c r="N14" t="n">
-        <v>-17.2688</v>
-      </c>
-      <c r="O14" t="n">
-        <v>-8.787800000000001</v>
-      </c>
-      <c r="P14" t="n">
-        <v>12.1471</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>-25.3068</v>
-      </c>
-      <c r="R14" t="n">
-        <v>37.4539</v>
-      </c>
-      <c r="S14" t="n">
-        <v>-3.098</v>
-      </c>
-      <c r="T14" t="n">
-        <v>-1.9074</v>
-      </c>
-      <c r="U14" t="n">
-        <v>-1.1906</v>
-      </c>
-      <c r="V14" t="n">
-        <v>5.3203</v>
-      </c>
-      <c r="W14" t="n">
-        <v>9.055300000000001</v>
-      </c>
-      <c r="X14" t="n">
         <v>-3.7351</v>
       </c>
     </row>
